--- a/docs/plantilla-cuestionario-completo.xlsx
+++ b/docs/plantilla-cuestionario-completo.xlsx
@@ -389,7 +389,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5183" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5179" uniqueCount="459">
   <si>
     <t>dimension_codigo</t>
   </si>
@@ -1552,7 +1552,7 @@
     <t>Opciones no aplicables</t>
   </si>
   <si>
-    <t>Las respuestas manuales por inexistencia de kiosco, comedor o jornada/albergue no se incluyeron en la hoja importable. Deben reemplazarse por exclusiones automáticas cuando se implemente y confirme la condicionalidad.</t>
+    <t>Las respuestas manuales por inexistencia de infraestructura no se incluyen en la hoja importable. p021-p027 se excluyen automáticamente cuando la ficha indica que la escuela no posee kiosco; la correspondencia exacta de comedor y jornada/albergue continúa pendiente de definición.</t>
   </si>
   <si>
     <t>Fuente consolidada</t>
@@ -1700,15 +1700,6 @@
   </si>
   <si>
     <t>La respuesta funcional final agrega “El establecimiento no cuenta con Comedor”. Se conserva en la hoja Fuente, pero no puede importarse como respuesta puntuable: confirmar si p020 debe excluirse automáticamente cuando no existe comedor.</t>
-  </si>
-  <si>
-    <t>21 a 27</t>
-  </si>
-  <si>
-    <t>Condición por kiosco</t>
-  </si>
-  <si>
-    <t>La respuesta funcional enumera p021–p027, pero más adelante dice que el filtro anula 9 preguntas sin identificar las dos adicionales. El backend aplica la definición enumerada de 7; falta resolver la contradicción antes de publicar.</t>
   </si>
   <si>
     <t>28 a 32</t>
@@ -12525,7 +12516,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -12595,97 +12586,83 @@
         <v>431</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>440</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="4" t="s">
         <v>441</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>211</v>
+        <v>243</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>443</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>444</v>
+        <v>422</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>445</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="C7" s="4" t="s">
+      <c r="D7" s="4" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
         <v>446</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>445</v>
-      </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="C8" s="9" t="s">
         <v>447</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="D8" s="9" t="s">
         <v>448</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
+    </row>
+    <row r="9" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>449</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>263</v>
-      </c>
-      <c r="C9" s="9" t="s">
+      <c r="D9" s="4" t="s">
         <v>450</v>
       </c>
-      <c r="D9" s="9" t="s">
+    </row>
+    <row r="10" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="9" t="s">
+        <v>446</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>371</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>447</v>
+      </c>
+      <c r="D10" s="9" t="s">
         <v>451</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>431</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>452</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
-        <v>449</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>371</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>450</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>454</v>
       </c>
     </row>
   </sheetData>
@@ -12752,7 +12729,7 @@
         <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12793,7 +12770,7 @@
         <v>16</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12834,7 +12811,7 @@
         <v>16</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12875,7 +12852,7 @@
         <v>16</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="5" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12916,7 +12893,7 @@
         <v>16</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="6" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12957,7 +12934,7 @@
         <v>16</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="7" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12998,7 +12975,7 @@
         <v>16</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="8" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13039,7 +13016,7 @@
         <v>16</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="9" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13080,7 +13057,7 @@
         <v>16</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="10" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13121,7 +13098,7 @@
         <v>16</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="11" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13162,7 +13139,7 @@
         <v>16</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="12" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13203,7 +13180,7 @@
         <v>16</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="13" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13244,7 +13221,7 @@
         <v>16</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="14" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13285,7 +13262,7 @@
         <v>16</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="15" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13326,7 +13303,7 @@
         <v>16</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="16" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13367,7 +13344,7 @@
         <v>16</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="17" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13408,7 +13385,7 @@
         <v>16</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="18" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13449,7 +13426,7 @@
         <v>16</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="19" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13490,7 +13467,7 @@
         <v>16</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="20" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13531,7 +13508,7 @@
         <v>16</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="21" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13572,7 +13549,7 @@
         <v>16</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="22" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13613,7 +13590,7 @@
         <v>16</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="23" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13654,7 +13631,7 @@
         <v>16</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="24" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13695,7 +13672,7 @@
         <v>16</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="25" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13736,7 +13713,7 @@
         <v>16</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="26" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13777,7 +13754,7 @@
         <v>16</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="27" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13818,7 +13795,7 @@
         <v>16</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="28" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13859,7 +13836,7 @@
         <v>16</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="29" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13900,7 +13877,7 @@
         <v>16</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="30" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13941,7 +13918,7 @@
         <v>16</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="31" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13982,7 +13959,7 @@
         <v>16</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="32" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14023,7 +14000,7 @@
         <v>16</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="33" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14064,7 +14041,7 @@
         <v>16</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="34" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14105,7 +14082,7 @@
         <v>16</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="35" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -14131,7 +14108,7 @@
         <v>246</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="I35" s="4" t="s">
         <v>16</v>
@@ -14146,7 +14123,7 @@
         <v>16</v>
       </c>
       <c r="M35" s="4" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
     </row>
     <row r="36" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14187,7 +14164,7 @@
         <v>16</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="37" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14228,7 +14205,7 @@
         <v>16</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="38" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14269,7 +14246,7 @@
         <v>16</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="39" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -14295,7 +14272,7 @@
         <v>246</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="I39" s="4" t="s">
         <v>16</v>
@@ -14310,7 +14287,7 @@
         <v>16</v>
       </c>
       <c r="M39" s="4" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
     </row>
     <row r="40" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14351,7 +14328,7 @@
         <v>16</v>
       </c>
       <c r="M40" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="41" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14392,7 +14369,7 @@
         <v>16</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="42" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14433,7 +14410,7 @@
         <v>16</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="43" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14474,7 +14451,7 @@
         <v>16</v>
       </c>
       <c r="M43" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="44" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14515,7 +14492,7 @@
         <v>16</v>
       </c>
       <c r="M44" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="45" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14556,7 +14533,7 @@
         <v>16</v>
       </c>
       <c r="M45" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="46" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14597,7 +14574,7 @@
         <v>16</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="47" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14638,7 +14615,7 @@
         <v>16</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="48" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14679,7 +14656,7 @@
         <v>16</v>
       </c>
       <c r="M48" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="49" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14720,7 +14697,7 @@
         <v>16</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="50" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14761,7 +14738,7 @@
         <v>16</v>
       </c>
       <c r="M50" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="51" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14802,7 +14779,7 @@
         <v>16</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="52" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14843,7 +14820,7 @@
         <v>16</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="53" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14884,7 +14861,7 @@
         <v>16</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="54" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14925,7 +14902,7 @@
         <v>16</v>
       </c>
       <c r="M54" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="55" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -14951,7 +14928,7 @@
         <v>246</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="I55" s="4" t="s">
         <v>16</v>
@@ -14966,7 +14943,7 @@
         <v>16</v>
       </c>
       <c r="M55" s="4" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
     </row>
     <row r="56" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15007,7 +14984,7 @@
         <v>16</v>
       </c>
       <c r="M56" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="57" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15048,7 +15025,7 @@
         <v>16</v>
       </c>
       <c r="M57" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="58" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15089,7 +15066,7 @@
         <v>16</v>
       </c>
       <c r="M58" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="59" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -15115,7 +15092,7 @@
         <v>246</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="I59" s="4" t="s">
         <v>16</v>
@@ -15130,7 +15107,7 @@
         <v>16</v>
       </c>
       <c r="M59" s="4" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
     </row>
     <row r="60" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15171,7 +15148,7 @@
         <v>16</v>
       </c>
       <c r="M60" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="61" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15212,7 +15189,7 @@
         <v>16</v>
       </c>
       <c r="M61" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="62" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15253,7 +15230,7 @@
         <v>16</v>
       </c>
       <c r="M62" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="63" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -15279,7 +15256,7 @@
         <v>246</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="I63" s="4" t="s">
         <v>16</v>
@@ -15294,7 +15271,7 @@
         <v>16</v>
       </c>
       <c r="M63" s="4" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
     </row>
     <row r="64" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15335,7 +15312,7 @@
         <v>16</v>
       </c>
       <c r="M64" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="65" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15376,7 +15353,7 @@
         <v>16</v>
       </c>
       <c r="M65" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="66" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15417,7 +15394,7 @@
         <v>16</v>
       </c>
       <c r="M66" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="67" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -15443,7 +15420,7 @@
         <v>246</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="I67" s="4" t="s">
         <v>16</v>
@@ -15458,7 +15435,7 @@
         <v>16</v>
       </c>
       <c r="M67" s="4" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
     </row>
     <row r="68" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15499,7 +15476,7 @@
         <v>16</v>
       </c>
       <c r="M68" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="69" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15540,7 +15517,7 @@
         <v>16</v>
       </c>
       <c r="M69" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="70" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15581,7 +15558,7 @@
         <v>16</v>
       </c>
       <c r="M70" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="71" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -15607,7 +15584,7 @@
         <v>246</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="I71" s="4" t="s">
         <v>16</v>
@@ -15622,7 +15599,7 @@
         <v>16</v>
       </c>
       <c r="M71" s="4" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
     </row>
     <row r="72" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15663,7 +15640,7 @@
         <v>16</v>
       </c>
       <c r="M72" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="73" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15704,7 +15681,7 @@
         <v>16</v>
       </c>
       <c r="M73" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="74" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -15730,7 +15707,7 @@
         <v>25</v>
       </c>
       <c r="H74" s="4" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="I74" s="4" t="s">
         <v>16</v>
@@ -15745,7 +15722,7 @@
         <v>16</v>
       </c>
       <c r="M74" s="4" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
     </row>
     <row r="75" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15786,7 +15763,7 @@
         <v>16</v>
       </c>
       <c r="M75" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="76" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15827,7 +15804,7 @@
         <v>16</v>
       </c>
       <c r="M76" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="77" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -15853,7 +15830,7 @@
         <v>25</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="I77" s="4" t="s">
         <v>16</v>
@@ -15868,7 +15845,7 @@
         <v>16</v>
       </c>
       <c r="M77" s="4" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
     </row>
     <row r="78" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15909,7 +15886,7 @@
         <v>16</v>
       </c>
       <c r="M78" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="79" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15950,7 +15927,7 @@
         <v>16</v>
       </c>
       <c r="M79" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="80" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15991,7 +15968,7 @@
         <v>16</v>
       </c>
       <c r="M80" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="81" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -16017,7 +15994,7 @@
         <v>246</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="I81" s="4" t="s">
         <v>16</v>
@@ -16032,7 +16009,7 @@
         <v>16</v>
       </c>
       <c r="M81" s="4" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
     </row>
     <row r="82" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -16073,7 +16050,7 @@
         <v>16</v>
       </c>
       <c r="M82" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="83" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -16114,7 +16091,7 @@
         <v>16</v>
       </c>
       <c r="M83" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="84" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -16140,7 +16117,7 @@
         <v>25</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="I84" s="4" t="s">
         <v>16</v>
@@ -16155,7 +16132,7 @@
         <v>16</v>
       </c>
       <c r="M84" s="4" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
     </row>
     <row r="85" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -16196,7 +16173,7 @@
         <v>16</v>
       </c>
       <c r="M85" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="86" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -16237,7 +16214,7 @@
         <v>16</v>
       </c>
       <c r="M86" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="87" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -16278,7 +16255,7 @@
         <v>16</v>
       </c>
       <c r="M87" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="88" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -16304,7 +16281,7 @@
         <v>246</v>
       </c>
       <c r="H88" s="4" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="I88" s="4" t="s">
         <v>16</v>
@@ -16319,7 +16296,7 @@
         <v>16</v>
       </c>
       <c r="M88" s="4" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
     </row>
     <row r="89" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -16360,7 +16337,7 @@
         <v>16</v>
       </c>
       <c r="M89" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="90" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -16401,7 +16378,7 @@
         <v>16</v>
       </c>
       <c r="M90" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="91" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -16442,7 +16419,7 @@
         <v>16</v>
       </c>
       <c r="M91" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="92" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -16468,7 +16445,7 @@
         <v>246</v>
       </c>
       <c r="H92" s="4" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="I92" s="4" t="s">
         <v>16</v>
@@ -16483,7 +16460,7 @@
         <v>16</v>
       </c>
       <c r="M92" s="4" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
     </row>
     <row r="93" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -16524,7 +16501,7 @@
         <v>16</v>
       </c>
       <c r="M93" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="94" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -16565,7 +16542,7 @@
         <v>16</v>
       </c>
       <c r="M94" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="95" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -16606,7 +16583,7 @@
         <v>16</v>
       </c>
       <c r="M95" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="96" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -16632,7 +16609,7 @@
         <v>246</v>
       </c>
       <c r="H96" s="4" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="I96" s="4" t="s">
         <v>16</v>
@@ -16647,7 +16624,7 @@
         <v>16</v>
       </c>
       <c r="M96" s="4" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
     </row>
     <row r="97" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -16688,7 +16665,7 @@
         <v>16</v>
       </c>
       <c r="M97" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="98" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -16729,7 +16706,7 @@
         <v>16</v>
       </c>
       <c r="M98" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="99" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -16770,7 +16747,7 @@
         <v>16</v>
       </c>
       <c r="M99" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="100" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -16796,7 +16773,7 @@
         <v>246</v>
       </c>
       <c r="H100" s="4" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="I100" s="4" t="s">
         <v>16</v>
@@ -16811,7 +16788,7 @@
         <v>16</v>
       </c>
       <c r="M100" s="4" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
     </row>
     <row r="101" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -16852,7 +16829,7 @@
         <v>16</v>
       </c>
       <c r="M101" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="102" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -16893,7 +16870,7 @@
         <v>16</v>
       </c>
       <c r="M102" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="103" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -16934,7 +16911,7 @@
         <v>16</v>
       </c>
       <c r="M103" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="104" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -16960,7 +16937,7 @@
         <v>246</v>
       </c>
       <c r="H104" s="4" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="I104" s="4" t="s">
         <v>16</v>
@@ -16975,7 +16952,7 @@
         <v>16</v>
       </c>
       <c r="M104" s="4" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
     </row>
     <row r="105" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17016,7 +16993,7 @@
         <v>16</v>
       </c>
       <c r="M105" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="106" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17057,7 +17034,7 @@
         <v>16</v>
       </c>
       <c r="M106" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="107" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17098,7 +17075,7 @@
         <v>16</v>
       </c>
       <c r="M107" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="108" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -17124,7 +17101,7 @@
         <v>246</v>
       </c>
       <c r="H108" s="4" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="I108" s="4" t="s">
         <v>16</v>
@@ -17139,7 +17116,7 @@
         <v>16</v>
       </c>
       <c r="M108" s="4" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
     </row>
     <row r="109" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17180,7 +17157,7 @@
         <v>16</v>
       </c>
       <c r="M109" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="110" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17221,7 +17198,7 @@
         <v>16</v>
       </c>
       <c r="M110" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="111" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17262,7 +17239,7 @@
         <v>16</v>
       </c>
       <c r="M111" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="112" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -17288,7 +17265,7 @@
         <v>246</v>
       </c>
       <c r="H112" s="4" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="I112" s="4" t="s">
         <v>16</v>
@@ -17303,7 +17280,7 @@
         <v>16</v>
       </c>
       <c r="M112" s="4" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
     </row>
     <row r="113" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17344,7 +17321,7 @@
         <v>16</v>
       </c>
       <c r="M113" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="114" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17385,7 +17362,7 @@
         <v>16</v>
       </c>
       <c r="M114" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="115" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17426,7 +17403,7 @@
         <v>16</v>
       </c>
       <c r="M115" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="116" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17467,7 +17444,7 @@
         <v>16</v>
       </c>
       <c r="M116" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="117" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17508,7 +17485,7 @@
         <v>16</v>
       </c>
       <c r="M117" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="118" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17549,7 +17526,7 @@
         <v>16</v>
       </c>
       <c r="M118" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="119" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17590,7 +17567,7 @@
         <v>16</v>
       </c>
       <c r="M119" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="120" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17631,7 +17608,7 @@
         <v>16</v>
       </c>
       <c r="M120" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="121" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17672,7 +17649,7 @@
         <v>16</v>
       </c>
       <c r="M121" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="122" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17713,7 +17690,7 @@
         <v>16</v>
       </c>
       <c r="M122" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="123" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17754,7 +17731,7 @@
         <v>16</v>
       </c>
       <c r="M123" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="124" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17795,7 +17772,7 @@
         <v>16</v>
       </c>
       <c r="M124" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="125" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17836,7 +17813,7 @@
         <v>16</v>
       </c>
       <c r="M125" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="126" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17877,7 +17854,7 @@
         <v>16</v>
       </c>
       <c r="M126" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="127" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17918,7 +17895,7 @@
         <v>16</v>
       </c>
       <c r="M127" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="128" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -17959,7 +17936,7 @@
         <v>16</v>
       </c>
       <c r="M128" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="129" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -18000,7 +17977,7 @@
         <v>16</v>
       </c>
       <c r="M129" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="130" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -18041,7 +18018,7 @@
         <v>16</v>
       </c>
       <c r="M130" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="131" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -18082,7 +18059,7 @@
         <v>16</v>
       </c>
       <c r="M131" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="132" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -18123,7 +18100,7 @@
         <v>16</v>
       </c>
       <c r="M132" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="133" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -18164,7 +18141,7 @@
         <v>16</v>
       </c>
       <c r="M133" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="134" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -18205,7 +18182,7 @@
         <v>16</v>
       </c>
       <c r="M134" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="135" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -18246,7 +18223,7 @@
         <v>16</v>
       </c>
       <c r="M135" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="136" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -18287,7 +18264,7 @@
         <v>16</v>
       </c>
       <c r="M136" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="137" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -18328,7 +18305,7 @@
         <v>16</v>
       </c>
       <c r="M137" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="138" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -18369,7 +18346,7 @@
         <v>16</v>
       </c>
       <c r="M138" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="139" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -18410,7 +18387,7 @@
         <v>16</v>
       </c>
       <c r="M139" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="140" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -18451,7 +18428,7 @@
         <v>16</v>
       </c>
       <c r="M140" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="141" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -18492,7 +18469,7 @@
         <v>16</v>
       </c>
       <c r="M141" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="142" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -18533,7 +18510,7 @@
         <v>16</v>
       </c>
       <c r="M142" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="143" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -18574,7 +18551,7 @@
         <v>16</v>
       </c>
       <c r="M143" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="144" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -18615,7 +18592,7 @@
         <v>16</v>
       </c>
       <c r="M144" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="145" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -18656,7 +18633,7 @@
         <v>16</v>
       </c>
       <c r="M145" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="146" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -18697,7 +18674,7 @@
         <v>16</v>
       </c>
       <c r="M146" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="147" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -18738,7 +18715,7 @@
         <v>16</v>
       </c>
       <c r="M147" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="148" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -18779,7 +18756,7 @@
         <v>16</v>
       </c>
       <c r="M148" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="149" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -18820,7 +18797,7 @@
         <v>16</v>
       </c>
       <c r="M149" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="150" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -18861,7 +18838,7 @@
         <v>16</v>
       </c>
       <c r="M150" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="151" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -18902,7 +18879,7 @@
         <v>16</v>
       </c>
       <c r="M151" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="152" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -18943,7 +18920,7 @@
         <v>16</v>
       </c>
       <c r="M152" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="153" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -18984,7 +18961,7 @@
         <v>16</v>
       </c>
       <c r="M153" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="154" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -19025,7 +19002,7 @@
         <v>16</v>
       </c>
       <c r="M154" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="155" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -19066,7 +19043,7 @@
         <v>16</v>
       </c>
       <c r="M155" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="156" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -19107,7 +19084,7 @@
         <v>16</v>
       </c>
       <c r="M156" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="157" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -19148,7 +19125,7 @@
         <v>16</v>
       </c>
       <c r="M157" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="158" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -19189,7 +19166,7 @@
         <v>16</v>
       </c>
       <c r="M158" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="159" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -19230,7 +19207,7 @@
         <v>16</v>
       </c>
       <c r="M159" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="160" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -19271,7 +19248,7 @@
         <v>16</v>
       </c>
       <c r="M160" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="161" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -19312,7 +19289,7 @@
         <v>16</v>
       </c>
       <c r="M161" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="162" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -19353,7 +19330,7 @@
         <v>16</v>
       </c>
       <c r="M162" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="163" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -19394,7 +19371,7 @@
         <v>16</v>
       </c>
       <c r="M163" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="164" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -19435,7 +19412,7 @@
         <v>16</v>
       </c>
       <c r="M164" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="165" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -19476,7 +19453,7 @@
         <v>16</v>
       </c>
       <c r="M165" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="166" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -19517,7 +19494,7 @@
         <v>16</v>
       </c>
       <c r="M166" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="167" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -19558,7 +19535,7 @@
         <v>16</v>
       </c>
       <c r="M167" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="168" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -19599,7 +19576,7 @@
         <v>16</v>
       </c>
       <c r="M168" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="169" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -19640,7 +19617,7 @@
         <v>16</v>
       </c>
       <c r="M169" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="170" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -19681,7 +19658,7 @@
         <v>16</v>
       </c>
       <c r="M170" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="171" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -19722,7 +19699,7 @@
         <v>16</v>
       </c>
       <c r="M171" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="172" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -19763,7 +19740,7 @@
         <v>16</v>
       </c>
       <c r="M172" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="173" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -19804,7 +19781,7 @@
         <v>16</v>
       </c>
       <c r="M173" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="174" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -19845,7 +19822,7 @@
         <v>16</v>
       </c>
       <c r="M174" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="175" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -19886,7 +19863,7 @@
         <v>16</v>
       </c>
       <c r="M175" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="176" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -19927,7 +19904,7 @@
         <v>16</v>
       </c>
       <c r="M176" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="177" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -19968,7 +19945,7 @@
         <v>16</v>
       </c>
       <c r="M177" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="178" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -20009,7 +19986,7 @@
         <v>16</v>
       </c>
       <c r="M178" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="179" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -20050,7 +20027,7 @@
         <v>16</v>
       </c>
       <c r="M179" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="180" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -20091,7 +20068,7 @@
         <v>16</v>
       </c>
       <c r="M180" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="181" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -20132,7 +20109,7 @@
         <v>16</v>
       </c>
       <c r="M181" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="182" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -20173,7 +20150,7 @@
         <v>16</v>
       </c>
       <c r="M182" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="183" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -20214,7 +20191,7 @@
         <v>16</v>
       </c>
       <c r="M183" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="184" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -20255,7 +20232,7 @@
         <v>16</v>
       </c>
       <c r="M184" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="185" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -20296,7 +20273,7 @@
         <v>16</v>
       </c>
       <c r="M185" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="186" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -20337,7 +20314,7 @@
         <v>16</v>
       </c>
       <c r="M186" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="187" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -20378,7 +20355,7 @@
         <v>16</v>
       </c>
       <c r="M187" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="188" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -20419,7 +20396,7 @@
         <v>16</v>
       </c>
       <c r="M188" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="189" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -20460,7 +20437,7 @@
         <v>16</v>
       </c>
       <c r="M189" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="190" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -20501,7 +20478,7 @@
         <v>16</v>
       </c>
       <c r="M190" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="191" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -20542,7 +20519,7 @@
         <v>16</v>
       </c>
       <c r="M191" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="192" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -20583,7 +20560,7 @@
         <v>16</v>
       </c>
       <c r="M192" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="193" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -20624,7 +20601,7 @@
         <v>16</v>
       </c>
       <c r="M193" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="194" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -20665,7 +20642,7 @@
         <v>16</v>
       </c>
       <c r="M194" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="195" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -20706,7 +20683,7 @@
         <v>16</v>
       </c>
       <c r="M195" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="196" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -20747,7 +20724,7 @@
         <v>16</v>
       </c>
       <c r="M196" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="197" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -20788,7 +20765,7 @@
         <v>16</v>
       </c>
       <c r="M197" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="198" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -20829,7 +20806,7 @@
         <v>16</v>
       </c>
       <c r="M198" s="4" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
   </sheetData>
